--- a/database/event/2684/event_2684_evp_summary.xlsx
+++ b/database/event/2684/event_2684_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6487</v>
+        <v>6.6694</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5043</v>
+        <v>3.5152</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2646</v>
+        <v>2.2132</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6487</v>
+        <v>6.6694</v>
       </c>
       <c r="F2" t="n">
-        <v>2.443</v>
+        <v>2.4637</v>
       </c>
       <c r="G2" t="n">
         <v>4.2057</v>
       </c>
       <c r="H2" t="n">
-        <v>2.443</v>
+        <v>2.4637</v>
       </c>
       <c r="I2" t="n">
-        <v>2.443</v>
+        <v>2.4637</v>
       </c>
       <c r="J2" t="n">
         <v>4.2057</v>
@@ -529,7 +529,7 @@
         <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6487</v>
+        <v>6.6694</v>
       </c>
       <c r="N2" t="n">
         <v>266</v>
@@ -548,7 +548,7 @@
         <v>3.2742</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0882</v>
+        <v>2.031</v>
       </c>
       <c r="E3" t="n">
         <v>6.2121</v>
@@ -594,7 +594,7 @@
         <v>2.4808</v>
       </c>
       <c r="D4" t="n">
-        <v>1.48</v>
+        <v>1.4312</v>
       </c>
       <c r="E4" t="n">
         <v>4.7067</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.994</v>
+        <v>4.3131</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1051</v>
+        <v>2.2733</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1921</v>
+        <v>1.2744</v>
       </c>
       <c r="E5" t="n">
-        <v>3.994</v>
+        <v>4.3131</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8401</v>
+        <v>2.1592</v>
       </c>
       <c r="G5" t="n">
         <v>2.1539</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8401</v>
+        <v>2.1592</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8401</v>
+        <v>2.1592</v>
       </c>
       <c r="J5" t="n">
         <v>2.1539</v>
@@ -667,7 +667,7 @@
         <v>149</v>
       </c>
       <c r="M5" t="n">
-        <v>3.994</v>
+        <v>4.3131</v>
       </c>
       <c r="N5" t="n">
         <v>267</v>
@@ -686,7 +686,7 @@
         <v>1.8641</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0074</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>3.5368</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1249</v>
+        <v>3.5162</v>
       </c>
       <c r="C7" t="n">
-        <v>1.647</v>
+        <v>1.8533</v>
       </c>
       <c r="D7" t="n">
-        <v>0.841</v>
+        <v>0.9569</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1249</v>
+        <v>3.5162</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7912</v>
+        <v>3.1825</v>
       </c>
       <c r="G7" t="n">
         <v>0.3337</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7912</v>
+        <v>3.1825</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8042</v>
+        <v>3.2093</v>
       </c>
       <c r="J7" t="n">
         <v>0.3337</v>
@@ -759,7 +759,7 @@
         <v>90</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1379</v>
+        <v>3.543</v>
       </c>
       <c r="N7" t="n">
         <v>234</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5308</v>
+        <v>3.4046</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3339</v>
+        <v>1.7945</v>
       </c>
       <c r="D8" t="n">
-        <v>0.601</v>
+        <v>0.9125</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5308</v>
+        <v>3.4046</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8921</v>
+        <v>2.7659</v>
       </c>
       <c r="G8" t="n">
         <v>0.6387</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8921</v>
+        <v>2.7659</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9009</v>
+        <v>2.7891</v>
       </c>
       <c r="J8" t="n">
         <v>0.6387</v>
@@ -805,7 +805,7 @@
         <v>90</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5396</v>
+        <v>3.4278</v>
       </c>
       <c r="N8" t="n">
         <v>234</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5207</v>
+        <v>3.1469</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3286</v>
+        <v>1.6586</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5969</v>
+        <v>0.8098</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5207</v>
+        <v>3.1469</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9267</v>
+        <v>1.9522</v>
       </c>
       <c r="G9" t="n">
-        <v>1.594</v>
+        <v>1.1947</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9267</v>
+        <v>1.9522</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9267</v>
+        <v>1.9522</v>
       </c>
       <c r="J9" t="n">
-        <v>1.594</v>
+        <v>1.1947</v>
       </c>
       <c r="K9" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="L9" t="n">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5207</v>
+        <v>3.1469</v>
       </c>
       <c r="N9" t="n">
-        <v>266</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3638</v>
+        <v>2.9468</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2459</v>
+        <v>1.5532</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5336</v>
+        <v>0.7301</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3638</v>
+        <v>2.9468</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3985</v>
+        <v>1.4392</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653</v>
+        <v>1.5076</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3985</v>
+        <v>1.4392</v>
       </c>
       <c r="I10" t="n">
-        <v>1.405</v>
+        <v>1.4392</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9653</v>
+        <v>1.5076</v>
       </c>
       <c r="K10" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="L10" t="n">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3703</v>
+        <v>2.9468</v>
       </c>
       <c r="N10" t="n">
-        <v>303</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3142</v>
+        <v>2.8138</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2197</v>
+        <v>1.4831</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5135</v>
+        <v>0.6771</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3142</v>
+        <v>2.8138</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1195</v>
+        <v>2.5844</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1947</v>
+        <v>0.2294</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1195</v>
+        <v>2.5844</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1195</v>
+        <v>2.6061</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1947</v>
+        <v>0.2294</v>
       </c>
       <c r="K11" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="L11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3142</v>
+        <v>2.8355</v>
       </c>
       <c r="N11" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1997</v>
+        <v>2.8089</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1594</v>
+        <v>1.4805</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4673</v>
+        <v>0.6752</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1997</v>
+        <v>2.8089</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1736</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>2.0261</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1736</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1744</v>
+        <v>0.7894</v>
       </c>
       <c r="J12" t="n">
         <v>2.0261</v>
@@ -989,7 +989,7 @@
         <v>107</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2005</v>
+        <v>2.8155</v>
       </c>
       <c r="N12" t="n">
         <v>303</v>
@@ -998,231 +998,231 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0745</v>
+        <v>2.6017</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0934</v>
+        <v>1.3713</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4167</v>
+        <v>0.5926</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0745</v>
+        <v>2.6017</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5669</v>
+        <v>2.6321</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5076</v>
+        <v>-0.0304</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5669</v>
+        <v>2.6321</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5669</v>
+        <v>2.6321</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5076</v>
+        <v>-0.0304</v>
       </c>
       <c r="K13" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="L13" t="n">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0745</v>
+        <v>2.6017</v>
       </c>
       <c r="N13" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9284</v>
+        <v>2.5207</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0164</v>
+        <v>1.3286</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3577</v>
+        <v>0.5603</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9284</v>
+        <v>2.5207</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9284</v>
+        <v>0.9267</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.594</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9284</v>
+        <v>0.9267</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9284</v>
+        <v>0.9267</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.594</v>
       </c>
       <c r="K14" t="n">
         <v>98</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9284</v>
+        <v>2.5207</v>
       </c>
       <c r="N14" t="n">
-        <v>98</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9258</v>
+        <v>2.3586</v>
       </c>
       <c r="C15" t="n">
-        <v>1.015</v>
+        <v>1.2431</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3566</v>
+        <v>0.4958</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9258</v>
+        <v>2.3586</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8511</v>
+        <v>1.3933</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0747</v>
+        <v>0.9653</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8511</v>
+        <v>1.3933</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8511</v>
+        <v>1.405</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0747</v>
+        <v>0.9653</v>
       </c>
       <c r="K15" t="n">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9258</v>
+        <v>2.3703</v>
       </c>
       <c r="N15" t="n">
-        <v>118</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8996</v>
+        <v>2.3022</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0012</v>
+        <v>1.2134</v>
       </c>
       <c r="D16" t="n">
-        <v>0.346</v>
+        <v>0.4733</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8996</v>
+        <v>2.3022</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6702</v>
+        <v>3.09</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2294</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6702</v>
+        <v>3.09</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6779</v>
+        <v>3.09</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2294</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="L16" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9073</v>
+        <v>2.3022</v>
       </c>
       <c r="N16" t="n">
-        <v>234</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8572</v>
+        <v>2.2422</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9789</v>
+        <v>1.1818</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3289</v>
+        <v>0.4494</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8572</v>
+        <v>2.2422</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7398</v>
+        <v>2.1675</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1174</v>
+        <v>0.0747</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7398</v>
+        <v>2.1675</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7398</v>
+        <v>2.1675</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1174</v>
+        <v>0.0747</v>
       </c>
       <c r="K17" t="n">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="L17" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8572</v>
+        <v>2.2422</v>
       </c>
       <c r="N17" t="n">
-        <v>210</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7968</v>
+        <v>2.1886</v>
       </c>
       <c r="C18" t="n">
-        <v>0.947</v>
+        <v>1.1535</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3045</v>
+        <v>0.428</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7968</v>
+        <v>2.1886</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7968</v>
+        <v>2.1886</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7968</v>
+        <v>2.1886</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7968</v>
+        <v>2.1886</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7968</v>
+        <v>2.1886</v>
       </c>
       <c r="N18" t="n">
         <v>129</v>
@@ -1274,737 +1274,737 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.777</v>
+        <v>2.0453</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9366</v>
+        <v>1.078</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2965</v>
+        <v>0.3709</v>
       </c>
       <c r="E19" t="n">
-        <v>1.777</v>
+        <v>2.0453</v>
       </c>
       <c r="F19" t="n">
-        <v>1.777</v>
+        <v>2.0453</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.777</v>
+        <v>2.0453</v>
       </c>
       <c r="I19" t="n">
-        <v>1.777</v>
+        <v>2.0453</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.777</v>
+        <v>2.0453</v>
       </c>
       <c r="N19" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7669</v>
+        <v>2.0329</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9313</v>
+        <v>1.0715</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2924</v>
+        <v>0.366</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7669</v>
+        <v>2.0329</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5377</v>
+        <v>2.0329</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2292</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5377</v>
+        <v>2.0329</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5377</v>
+        <v>2.0329</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2292</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7669</v>
+        <v>2.0329</v>
       </c>
       <c r="N20" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7066</v>
+        <v>1.9995</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8995</v>
+        <v>1.0539</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2681</v>
+        <v>0.3527</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7066</v>
+        <v>1.9995</v>
       </c>
       <c r="F21" t="n">
-        <v>1.737</v>
+        <v>0.8821</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0304</v>
+        <v>1.1174</v>
       </c>
       <c r="H21" t="n">
-        <v>1.737</v>
+        <v>0.8821</v>
       </c>
       <c r="I21" t="n">
-        <v>1.737</v>
+        <v>0.8821</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0304</v>
+        <v>1.1174</v>
       </c>
       <c r="K21" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L21" t="n">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7066</v>
+        <v>1.9995</v>
       </c>
       <c r="N21" t="n">
-        <v>267</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6588</v>
+        <v>1.9515</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8743</v>
+        <v>1.0286</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2488</v>
+        <v>0.3336</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6588</v>
+        <v>1.9515</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0854</v>
+        <v>1.2578</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5734</v>
+        <v>0.6937</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0854</v>
+        <v>1.2578</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0854</v>
+        <v>1.2684</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5734</v>
+        <v>0.6937</v>
       </c>
       <c r="K22" t="n">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="L22" t="n">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6588</v>
+        <v>1.9621</v>
       </c>
       <c r="N22" t="n">
-        <v>266</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6582</v>
+        <v>1.8763</v>
       </c>
       <c r="C23" t="n">
-        <v>0.874</v>
+        <v>0.9889</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2485</v>
+        <v>0.3036</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6582</v>
+        <v>1.8763</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2041</v>
+        <v>1.8763</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5459000000000001</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2041</v>
+        <v>1.8763</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2041</v>
+        <v>1.8763</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5459000000000001</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6582</v>
+        <v>1.8763</v>
       </c>
       <c r="N23" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4999</v>
+        <v>1.8732</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7906</v>
+        <v>0.9873</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1846</v>
+        <v>0.3024</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4999</v>
+        <v>1.8732</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4999</v>
+        <v>1.644</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4999</v>
+        <v>1.644</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4999</v>
+        <v>1.644</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="K24" t="n">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4999</v>
+        <v>1.8732</v>
       </c>
       <c r="N24" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4462</v>
+        <v>1.8281</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7622</v>
+        <v>0.9635</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1629</v>
+        <v>0.2844</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4462</v>
+        <v>1.8281</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4462</v>
+        <v>2.8053</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>-0.9772</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4462</v>
+        <v>2.8053</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4462</v>
+        <v>2.8053</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>-0.9772</v>
       </c>
       <c r="K25" t="n">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="L25" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4462</v>
+        <v>1.8281</v>
       </c>
       <c r="N25" t="n">
-        <v>118</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3822</v>
+        <v>1.6588</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7285</v>
+        <v>0.8743</v>
       </c>
       <c r="D26" t="n">
-        <v>0.137</v>
+        <v>0.217</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3822</v>
+        <v>1.6588</v>
       </c>
       <c r="F26" t="n">
-        <v>2.17</v>
+        <v>0.0854</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7877999999999999</v>
+        <v>1.5734</v>
       </c>
       <c r="H26" t="n">
-        <v>2.17</v>
+        <v>0.0854</v>
       </c>
       <c r="I26" t="n">
-        <v>2.17</v>
+        <v>0.0854</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7877999999999999</v>
+        <v>1.5734</v>
       </c>
       <c r="K26" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="L26" t="n">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3822</v>
+        <v>1.6588</v>
       </c>
       <c r="N26" t="n">
-        <v>118</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3302</v>
+        <v>1.6582</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.874</v>
       </c>
       <c r="D27" t="n">
-        <v>0.116</v>
+        <v>0.2167</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3302</v>
+        <v>1.6582</v>
       </c>
       <c r="F27" t="n">
-        <v>2.3074</v>
+        <v>2.2041</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9772</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3074</v>
+        <v>2.2041</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3074</v>
+        <v>2.2041</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9772</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="L27" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3302</v>
+        <v>1.6582</v>
       </c>
       <c r="N27" t="n">
-        <v>210</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3212</v>
+        <v>1.6409</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6964</v>
+        <v>0.8649</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1124</v>
+        <v>0.2098</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3212</v>
+        <v>1.6409</v>
       </c>
       <c r="F28" t="n">
-        <v>2.3212</v>
+        <v>1.6409</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3212</v>
+        <v>1.6409</v>
       </c>
       <c r="I28" t="n">
-        <v>2.332</v>
+        <v>1.6409</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="L28" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.332</v>
+        <v>1.6409</v>
       </c>
       <c r="N28" t="n">
-        <v>222</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1994</v>
+        <v>1.5385</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6322</v>
+        <v>0.8109</v>
       </c>
       <c r="D29" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1994</v>
+        <v>1.5385</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7508</v>
+        <v>2.5385</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5514</v>
+        <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7508</v>
+        <v>2.5385</v>
       </c>
       <c r="I29" t="n">
-        <v>1.759</v>
+        <v>2.5385</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5514</v>
+        <v>-1</v>
       </c>
       <c r="K29" t="n">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="L29" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2076</v>
+        <v>1.5385</v>
       </c>
       <c r="N29" t="n">
-        <v>222</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1138</v>
+        <v>1.3125</v>
       </c>
       <c r="C30" t="n">
-        <v>0.587</v>
+        <v>0.6918</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0286</v>
+        <v>0.079</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1138</v>
+        <v>1.3125</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4201</v>
+        <v>2.3125</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6937</v>
+        <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4201</v>
+        <v>2.3125</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4221</v>
+        <v>2.332</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6937</v>
+        <v>-1</v>
       </c>
       <c r="K30" t="n">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="L30" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1158</v>
+        <v>1.332</v>
       </c>
       <c r="N30" t="n">
-        <v>303</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0982</v>
+        <v>1.2932</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5788</v>
+        <v>0.6816</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0223</v>
+        <v>0.0713</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0982</v>
+        <v>1.2932</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0982</v>
+        <v>1.2932</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0982</v>
+        <v>1.2932</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0982</v>
+        <v>1.2932</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0982</v>
+        <v>1.2932</v>
       </c>
       <c r="N31" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8914</v>
+        <v>1.2035</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4698</v>
+        <v>0.6343</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0613</v>
+        <v>0.0356</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8914</v>
+        <v>1.2035</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6385999999999999</v>
+        <v>1.2035</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2528</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6385999999999999</v>
+        <v>1.2035</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.2035</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2528</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="L32" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8944</v>
+        <v>1.2035</v>
       </c>
       <c r="N32" t="n">
-        <v>234</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7989000000000001</v>
+        <v>1.1929</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4211</v>
+        <v>0.6287</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.0313</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7989000000000001</v>
+        <v>1.1929</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6977</v>
+        <v>1.7443</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1012</v>
+        <v>-0.5514</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6977</v>
+        <v>1.7443</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6977</v>
+        <v>1.759</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1012</v>
+        <v>-0.5514</v>
       </c>
       <c r="K33" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="L33" t="n">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7988999999999999</v>
+        <v>1.2076</v>
       </c>
       <c r="N33" t="n">
-        <v>267</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7468</v>
+        <v>1.0618</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3936</v>
+        <v>0.5596</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1197</v>
+        <v>-0.0209</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7468</v>
+        <v>1.0618</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3642</v>
+        <v>1.0618</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3826</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3642</v>
+        <v>1.0618</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3642</v>
+        <v>1.0618</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3826</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L34" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7468</v>
+        <v>1.0618</v>
       </c>
       <c r="N34" t="n">
-        <v>266</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7164</v>
+        <v>0.9418</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3776</v>
+        <v>0.4964</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.132</v>
+        <v>-0.0687</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7164</v>
+        <v>0.9418</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7164</v>
+        <v>0.9418</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7164</v>
+        <v>0.9418</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7164</v>
+        <v>0.9418</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7164</v>
+        <v>0.9418</v>
       </c>
       <c r="N35" t="n">
         <v>109</v>
@@ -2056,860 +2056,860 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6567</v>
+        <v>0.889</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3461</v>
+        <v>0.4686</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1561</v>
+        <v>-0.0897</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6567</v>
+        <v>0.889</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6567</v>
+        <v>0.6362</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.2528</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6567</v>
+        <v>0.6362</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6567</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.2528</v>
       </c>
       <c r="K36" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6567</v>
+        <v>0.8944</v>
       </c>
       <c r="N36" t="n">
-        <v>129</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6542</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3448</v>
+        <v>0.4211</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1571</v>
+        <v>-0.1256</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6542</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6542</v>
+        <v>0.6977</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.1012</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6542</v>
+        <v>0.6977</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6542</v>
+        <v>0.6977</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.1012</v>
       </c>
       <c r="K37" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6542</v>
+        <v>0.7988999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>96</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5379</v>
+        <v>0.7468</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2835</v>
+        <v>0.3936</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2041</v>
+        <v>-0.1464</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5379</v>
+        <v>0.7468</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5379</v>
+        <v>0.3642</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.3826</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5379</v>
+        <v>0.3642</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5379</v>
+        <v>0.3642</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.3826</v>
       </c>
       <c r="K38" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5379</v>
+        <v>0.7468</v>
       </c>
       <c r="N38" t="n">
-        <v>58</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5325</v>
+        <v>0.6553</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2807</v>
+        <v>0.3454</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2062</v>
+        <v>-0.1828</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5325</v>
+        <v>0.6553</v>
       </c>
       <c r="F39" t="n">
-        <v>1.6428</v>
+        <v>-0.1638</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1103</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>1.6428</v>
+        <v>-0.1638</v>
       </c>
       <c r="I39" t="n">
-        <v>1.6428</v>
+        <v>-0.1652</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.1103</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="L39" t="n">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5325</v>
+        <v>0.6539</v>
       </c>
       <c r="N39" t="n">
-        <v>267</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5179</v>
+        <v>0.5379</v>
       </c>
       <c r="C40" t="n">
-        <v>0.273</v>
+        <v>0.2835</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2121</v>
+        <v>-0.2296</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5179</v>
+        <v>0.5379</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3491</v>
+        <v>0.5379</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1688</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3491</v>
+        <v>0.5379</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491</v>
+        <v>0.5379</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1688</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="L40" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5179</v>
+        <v>0.5379</v>
       </c>
       <c r="N40" t="n">
-        <v>316</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4637</v>
+        <v>0.5325</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2444</v>
+        <v>0.2807</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.234</v>
+        <v>-0.2318</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4637</v>
+        <v>0.5325</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0537</v>
+        <v>1.6428</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.59</v>
+        <v>-1.1103</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0537</v>
+        <v>1.6428</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0537</v>
+        <v>1.6428</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.59</v>
+        <v>-1.1103</v>
       </c>
       <c r="K41" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L41" t="n">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4637000000000001</v>
+        <v>0.5325</v>
       </c>
       <c r="N41" t="n">
-        <v>210</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4632</v>
+        <v>0.5179</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2441</v>
+        <v>0.273</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2342</v>
+        <v>-0.2376</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4632</v>
+        <v>0.5179</v>
       </c>
       <c r="F42" t="n">
-        <v>1.1537</v>
+        <v>0.3491</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.6905</v>
+        <v>0.1688</v>
       </c>
       <c r="H42" t="n">
-        <v>1.1537</v>
+        <v>0.3491</v>
       </c>
       <c r="I42" t="n">
-        <v>1.159</v>
+        <v>0.3491</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.6905</v>
+        <v>0.1688</v>
       </c>
       <c r="K42" t="n">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="L42" t="n">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4685</v>
+        <v>0.5179</v>
       </c>
       <c r="N42" t="n">
-        <v>222</v>
+        <v>316</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4196</v>
+        <v>0.4637</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2212</v>
+        <v>0.2444</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2519</v>
+        <v>-0.2592</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4196</v>
+        <v>0.4637</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4196</v>
+        <v>1.0537</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4196</v>
+        <v>1.0537</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4196</v>
+        <v>1.0537</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="K43" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4196</v>
+        <v>0.4637000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>98</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2716</v>
+        <v>0.4589</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1432</v>
+        <v>0.2419</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3116</v>
+        <v>-0.2611</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2716</v>
+        <v>0.4589</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2716</v>
+        <v>1.1494</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.6905</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2716</v>
+        <v>1.1494</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2716</v>
+        <v>1.159</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.6905</v>
       </c>
       <c r="K44" t="n">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2716</v>
+        <v>0.4685</v>
       </c>
       <c r="N44" t="n">
-        <v>109</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2276</v>
+        <v>0.2976</v>
       </c>
       <c r="C45" t="n">
-        <v>0.12</v>
+        <v>0.1569</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3294</v>
+        <v>-0.3253</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2276</v>
+        <v>0.2976</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.5915</v>
+        <v>0.2976</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8191000000000001</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.5915</v>
+        <v>0.2976</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5943000000000001</v>
+        <v>0.2976</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8191000000000001</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="L45" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2248</v>
+        <v>0.2976</v>
       </c>
       <c r="N45" t="n">
-        <v>222</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2039</v>
+        <v>0.2609</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1075</v>
+        <v>0.1375</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.339</v>
+        <v>-0.34</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2039</v>
+        <v>0.2609</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2039</v>
+        <v>0.2609</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2039</v>
+        <v>0.2609</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2039</v>
+        <v>0.2609</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2039</v>
+        <v>0.2609</v>
       </c>
       <c r="N46" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1977</v>
+        <v>0.2126</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1042</v>
+        <v>0.1121</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3415</v>
+        <v>-0.3592</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1977</v>
+        <v>0.2126</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.8987000000000001</v>
+        <v>0.2126</v>
       </c>
       <c r="G47" t="n">
-        <v>1.0964</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8987000000000001</v>
+        <v>0.2126</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8987000000000001</v>
+        <v>0.2126</v>
       </c>
       <c r="J47" t="n">
-        <v>1.0964</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L47" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1977</v>
+        <v>0.2126</v>
       </c>
       <c r="N47" t="n">
-        <v>316</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1853</v>
+        <v>0.2039</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0977</v>
+        <v>0.1075</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3465</v>
+        <v>-0.3627</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1853</v>
+        <v>0.2039</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1853</v>
+        <v>0.2039</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1853</v>
+        <v>0.2039</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1853</v>
+        <v>0.2039</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1853</v>
+        <v>0.2039</v>
       </c>
       <c r="N48" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1595</v>
+        <v>0.1977</v>
       </c>
       <c r="C49" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1042</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3569</v>
+        <v>-0.3651</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1595</v>
+        <v>0.1977</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1595</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1.0964</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1595</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1595</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1.0964</v>
       </c>
       <c r="K49" t="n">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1595</v>
+        <v>0.1977</v>
       </c>
       <c r="N49" t="n">
-        <v>58</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.03</v>
+        <v>0.1853</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0158</v>
+        <v>0.0977</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4092</v>
+        <v>-0.3701</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03</v>
+        <v>0.1853</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03</v>
+        <v>0.1853</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.03</v>
+        <v>0.1853</v>
       </c>
       <c r="I50" t="n">
-        <v>0.03</v>
+        <v>0.1853</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03</v>
+        <v>0.1853</v>
       </c>
       <c r="N50" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0008</v>
+        <v>0.1595</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0004</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.421</v>
+        <v>-0.3804</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0008</v>
+        <v>0.1595</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0008</v>
+        <v>0.1595</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0008</v>
+        <v>0.1595</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0008</v>
+        <v>0.1595</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0008</v>
+        <v>0.1595</v>
       </c>
       <c r="N51" t="n">
-        <v>129</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0152</v>
+        <v>0.03</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.008</v>
+        <v>0.0158</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4275</v>
+        <v>-0.432</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0152</v>
+        <v>0.03</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0152</v>
+        <v>0.03</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0152</v>
+        <v>0.03</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0152</v>
+        <v>0.03</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0152</v>
+        <v>0.03</v>
       </c>
       <c r="N52" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0346</v>
+        <v>0.0004</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4479</v>
+        <v>-0.4436</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.0008</v>
       </c>
       <c r="N53" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1121</v>
+        <v>-0.0152</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0591</v>
+        <v>-0.008</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4666</v>
+        <v>-0.45</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1121</v>
+        <v>-0.0152</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1121</v>
+        <v>-0.0152</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1121</v>
+        <v>-0.0152</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1121</v>
+        <v>-0.0152</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1121</v>
+        <v>-0.0152</v>
       </c>
       <c r="N54" t="n">
         <v>96</v>
@@ -2930,354 +2930,354 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>moxie</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1859</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.098</v>
+        <v>-0.0346</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4965</v>
+        <v>-0.4701</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1859</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1859</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1859</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1859</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1859</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1944</v>
+        <v>-0.0838</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1025</v>
+        <v>-0.0442</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4999</v>
+        <v>-0.4773</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1944</v>
+        <v>-0.0838</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3994</v>
+        <v>-0.0838</v>
       </c>
       <c r="G56" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3994</v>
+        <v>-0.0838</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4013</v>
+        <v>-0.0838</v>
       </c>
       <c r="J56" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="L56" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.1963</v>
+        <v>-0.0838</v>
       </c>
       <c r="N56" t="n">
-        <v>303</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>moxie</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1952</v>
+        <v>-0.1859</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1029</v>
+        <v>-0.098</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5002</v>
+        <v>-0.518</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1952</v>
+        <v>-0.1859</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2234</v>
+        <v>-0.1859</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.4186</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2234</v>
+        <v>-0.1859</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2234</v>
+        <v>-0.1859</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.4186</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="L57" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1952</v>
+        <v>-0.1859</v>
       </c>
       <c r="N57" t="n">
-        <v>316</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2523</v>
+        <v>-0.193</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.133</v>
+        <v>-0.1017</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5233</v>
+        <v>-0.5208</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2523</v>
+        <v>-0.193</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2523</v>
+        <v>-0.398</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2523</v>
+        <v>-0.398</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2523</v>
+        <v>-0.4013</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
       <c r="K58" t="n">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2523</v>
+        <v>-0.1963</v>
       </c>
       <c r="N58" t="n">
-        <v>109</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2697</v>
+        <v>-0.1952</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1422</v>
+        <v>-0.1029</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5303</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2697</v>
+        <v>-0.1952</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2697</v>
+        <v>0.2234</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.4186</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2697</v>
+        <v>0.2234</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2697</v>
+        <v>0.2234</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.4186</v>
       </c>
       <c r="K59" t="n">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2697</v>
+        <v>-0.1952</v>
       </c>
       <c r="N59" t="n">
-        <v>58</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3842</v>
+        <v>-0.2523</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2025</v>
+        <v>-0.133</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5766</v>
+        <v>-0.5444</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3842</v>
+        <v>-0.2523</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3842</v>
+        <v>-0.2523</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3842</v>
+        <v>-0.2523</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3842</v>
+        <v>-0.2523</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3842</v>
+        <v>-0.2523</v>
       </c>
       <c r="N60" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4234</v>
+        <v>-0.2697</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2232</v>
+        <v>-0.1422</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5924</v>
+        <v>-0.5514</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4234</v>
+        <v>-0.2697</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4234</v>
+        <v>-0.2697</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4234</v>
+        <v>-0.2697</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4234</v>
+        <v>-0.2697</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.4234</v>
+        <v>-0.2697</v>
       </c>
       <c r="N61" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4757</v>
+        <v>-0.4234</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2507</v>
+        <v>-0.2232</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6135</v>
+        <v>-0.6126</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4757</v>
+        <v>-0.4234</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4757</v>
+        <v>-0.4234</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4757</v>
+        <v>-0.4234</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4757</v>
+        <v>-0.4234</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4757</v>
+        <v>-0.4234</v>
       </c>
       <c r="N62" t="n">
         <v>43</v>
@@ -3298,93 +3298,93 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>splashske</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4786</v>
+        <v>-0.4757</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2523</v>
+        <v>-0.2507</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6147</v>
+        <v>-0.6334</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4786</v>
+        <v>-0.4757</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4786</v>
+        <v>-0.4757</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4786</v>
+        <v>-0.4757</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4786</v>
+        <v>-0.4757</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4786</v>
+        <v>-0.4757</v>
       </c>
       <c r="N63" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>splashske</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.533</v>
+        <v>-0.4786</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2809</v>
+        <v>-0.2523</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6367</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.533</v>
+        <v>-0.4786</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.533</v>
+        <v>-0.4786</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.533</v>
+        <v>-0.4786</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.533</v>
+        <v>-0.4786</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.533</v>
+        <v>-0.4786</v>
       </c>
       <c r="N64" t="n">
-        <v>98</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -3400,7 +3400,7 @@
         <v>-0.3162</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6637</v>
+        <v>-0.6829</v>
       </c>
       <c r="E65" t="n">
         <v>-0.5999</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6182</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3258</v>
+        <v>-0.3254</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6711</v>
+        <v>-0.6899</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6182</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2034</v>
+        <v>-0.2026</v>
       </c>
       <c r="G66" t="n">
         <v>-0.4148</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2034</v>
+        <v>-0.2026</v>
       </c>
       <c r="I66" t="n">
         <v>-0.2043</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3306</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6747</v>
+        <v>-0.6938</v>
       </c>
       <c r="E67" t="n">
         <v>-0.6272</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4153</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7397</v>
+        <v>-0.7578</v>
       </c>
       <c r="E68" t="n">
         <v>-0.7879</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4539</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7693</v>
+        <v>-0.787</v>
       </c>
       <c r="E69" t="n">
         <v>-0.8612</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4888</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.796</v>
+        <v>-0.8133</v>
       </c>
       <c r="E70" t="n">
         <v>-0.9273</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5548</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8466</v>
+        <v>-0.8633</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0527</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6249</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9003</v>
+        <v>-0.9163</v>
       </c>
       <c r="E72" t="n">
         <v>-1.1856</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6483</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9183</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2301</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6704</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9352</v>
+        <v>-0.9506</v>
       </c>
       <c r="E74" t="n">
         <v>-1.2719</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6905</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9506</v>
+        <v>-0.9658</v>
       </c>
       <c r="E75" t="n">
         <v>-1.31</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7038</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9608</v>
+        <v>-0.9759</v>
       </c>
       <c r="E76" t="n">
         <v>-1.3354</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9341</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1373</v>
+        <v>-1.15</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7722</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9674</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1628</v>
+        <v>-1.1751</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8354</v>
@@ -4044,7 +4044,7 @@
         <v>-0.9878</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1785</v>
+        <v>-1.1906</v>
       </c>
       <c r="E79" t="n">
         <v>-1.8742</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.2441</v>
+        <v>-2.2379</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.1828</v>
+        <v>-1.1795</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3279</v>
+        <v>-1.3355</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.2441</v>
+        <v>-2.2379</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.6711</v>
+        <v>-1.6649</v>
       </c>
       <c r="G80" t="n">
         <v>-0.573</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.6711</v>
+        <v>-1.6649</v>
       </c>
       <c r="I80" t="n">
         <v>-1.6789</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.2651</v>
+        <v>-2.2573</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1939</v>
+        <v>-1.1898</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3364</v>
+        <v>-1.3432</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.2651</v>
+        <v>-2.2573</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.0899</v>
+        <v>-2.0821</v>
       </c>
       <c r="G81" t="n">
         <v>-0.1752</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.0899</v>
+        <v>-2.0821</v>
       </c>
       <c r="I81" t="n">
         <v>-2.0996</v>
